--- a/reports/Pioneer_Innovator_Sources_AUTO.xlsx
+++ b/reports/Pioneer_Innovator_Sources_AUTO.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>WEF UpLink Innovation Challenges (auto-discovered 2026-10-07)</t>
+          <t>WEF UpLink Innovation Challenges (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>WEF UpLink Innovation Challenges (auto-discovered 2026-10-07)</t>
+          <t>WEF UpLink Innovation Challenges (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>WEF UpLink Innovation Challenges (auto-discovered 2026-10-07)</t>
+          <t>WEF UpLink Innovation Challenges (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6532,7 +6532,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7104,7 +7104,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -7588,7 +7588,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -8908,7 +8908,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -9040,7 +9040,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -9392,7 +9392,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -9568,7 +9568,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -9788,7 +9788,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -10052,7 +10052,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -10272,7 +10272,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -10448,7 +10448,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -10580,7 +10580,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -10624,7 +10624,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -10668,7 +10668,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -10712,7 +10712,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -10932,7 +10932,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -11020,7 +11020,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -11108,7 +11108,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -11152,7 +11152,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -11196,7 +11196,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -11328,7 +11328,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -11372,7 +11372,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -11416,7 +11416,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -11460,7 +11460,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -11504,7 +11504,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -11636,7 +11636,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -11680,7 +11680,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -11724,7 +11724,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -11812,7 +11812,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -11900,7 +11900,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -11944,7 +11944,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -11988,7 +11988,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -12032,7 +12032,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -12208,7 +12208,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -12296,7 +12296,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -12340,7 +12340,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -12384,7 +12384,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -12516,7 +12516,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -12604,7 +12604,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -12692,7 +12692,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -12912,7 +12912,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -12956,7 +12956,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -13044,7 +13044,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -13088,7 +13088,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -13132,7 +13132,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -13264,7 +13264,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -13396,7 +13396,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -13440,7 +13440,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -13484,7 +13484,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -13528,7 +13528,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -13660,7 +13660,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -13748,7 +13748,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -13792,7 +13792,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -13836,7 +13836,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -13924,7 +13924,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -13968,7 +13968,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -14012,7 +14012,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -14100,7 +14100,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -14144,7 +14144,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -14188,7 +14188,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -14232,7 +14232,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -14276,7 +14276,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -14320,7 +14320,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -14408,7 +14408,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -14496,7 +14496,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -14540,7 +14540,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -14628,7 +14628,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -14672,7 +14672,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -14716,7 +14716,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -14760,7 +14760,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -14804,7 +14804,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -14848,7 +14848,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-07)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -14892,7 +14892,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-07)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -14936,7 +14936,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-07)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -14980,7 +14980,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-07)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -15024,7 +15024,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-07)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -15068,7 +15068,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-07)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -15112,7 +15112,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-07)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -15156,7 +15156,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-07)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -15200,7 +15200,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-07)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -15244,7 +15244,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-07)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -15288,7 +15288,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-07)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -15332,7 +15332,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -15420,7 +15420,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -15464,7 +15464,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -15508,7 +15508,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -15552,7 +15552,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -15596,7 +15596,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -15640,7 +15640,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -15684,7 +15684,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -15728,7 +15728,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -15772,7 +15772,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -15816,7 +15816,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -15860,7 +15860,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -15948,7 +15948,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -15992,7 +15992,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -16036,7 +16036,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -16080,7 +16080,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -16124,7 +16124,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -16168,7 +16168,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -16235,7 +16235,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>The TradFi-DeFi Market Map</t>
+          <t>State of AI Q3’26</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -16256,7 +16256,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -16279,7 +16279,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>State of Venture Q3’26</t>
+          <t>The TradFi-DeFi Market Map</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -16300,7 +16300,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -16344,7 +16344,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -16388,7 +16388,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -16432,7 +16432,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -16476,7 +16476,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -16520,7 +16520,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -16564,7 +16564,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -16608,7 +16608,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -16652,7 +16652,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -16696,7 +16696,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -16740,7 +16740,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -16784,7 +16784,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -16828,7 +16828,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -16916,7 +16916,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -16960,7 +16960,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -17004,7 +17004,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -17048,7 +17048,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -17092,7 +17092,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -17180,7 +17180,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -17224,7 +17224,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -17268,7 +17268,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -17312,7 +17312,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -17356,7 +17356,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -17400,7 +17400,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -17488,7 +17488,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -17576,7 +17576,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -17725,7 +17725,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -17806,7 +17806,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -17887,7 +17887,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -17968,7 +17968,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -18049,7 +18049,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -18130,7 +18130,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -18211,7 +18211,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -18292,7 +18292,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -18373,7 +18373,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -18454,7 +18454,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -18535,7 +18535,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -18616,7 +18616,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -18697,7 +18697,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -18778,7 +18778,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -18859,7 +18859,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -18940,7 +18940,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -19021,7 +19021,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -19102,7 +19102,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -19183,7 +19183,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -19345,7 +19345,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -19426,7 +19426,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -19507,7 +19507,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -19588,7 +19588,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -19669,7 +19669,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -19750,7 +19750,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -19831,7 +19831,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -19912,7 +19912,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -19993,7 +19993,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -20074,7 +20074,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -20155,7 +20155,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -20236,7 +20236,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -20317,7 +20317,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -20398,7 +20398,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -20479,7 +20479,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -20560,7 +20560,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -20641,7 +20641,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -20722,7 +20722,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -20803,7 +20803,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -20884,7 +20884,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-07)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -20965,7 +20965,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -21046,7 +21046,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -21127,7 +21127,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -21208,7 +21208,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -21289,7 +21289,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -21370,7 +21370,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -21451,7 +21451,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -21532,7 +21532,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -21613,7 +21613,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -21694,7 +21694,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -21775,7 +21775,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -21856,7 +21856,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -21937,7 +21937,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -22018,7 +22018,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -22099,7 +22099,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -22180,7 +22180,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -22261,7 +22261,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -22342,7 +22342,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -22504,7 +22504,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -22585,7 +22585,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -22666,7 +22666,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -22747,7 +22747,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -22828,7 +22828,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -22909,7 +22909,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -22990,7 +22990,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -23071,7 +23071,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -23152,7 +23152,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -23233,7 +23233,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -23314,7 +23314,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -23395,7 +23395,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -23476,7 +23476,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -23557,7 +23557,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -23638,7 +23638,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -23719,7 +23719,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -23800,7 +23800,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -23881,7 +23881,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -23962,7 +23962,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -24043,7 +24043,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -24124,7 +24124,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-07)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -24205,7 +24205,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -24286,7 +24286,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -24367,7 +24367,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -24448,7 +24448,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -24529,7 +24529,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -24610,7 +24610,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -24691,7 +24691,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -24772,7 +24772,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -24853,7 +24853,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -25015,7 +25015,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -25096,7 +25096,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -25177,7 +25177,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -25258,7 +25258,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -25339,7 +25339,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -25420,7 +25420,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -25501,7 +25501,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -25582,7 +25582,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -25663,7 +25663,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -25744,7 +25744,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -25825,7 +25825,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -25906,7 +25906,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -25987,7 +25987,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -26068,7 +26068,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -26149,7 +26149,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -26230,7 +26230,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -26311,7 +26311,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -26392,7 +26392,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -26473,7 +26473,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -26554,7 +26554,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -26635,7 +26635,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -26716,7 +26716,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -26797,7 +26797,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -26878,7 +26878,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -26959,7 +26959,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -27040,7 +27040,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -27121,7 +27121,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -27202,7 +27202,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -27283,7 +27283,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -27364,7 +27364,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-07)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -27445,7 +27445,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>WEF UpLink Innovation Challenges (auto-discovered 2026-10-07)</t>
+          <t>WEF UpLink Innovation Challenges (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -27526,7 +27526,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>WEF UpLink Innovation Challenges (auto-discovered 2026-10-07)</t>
+          <t>WEF UpLink Innovation Challenges (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -27607,7 +27607,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>WEF UpLink Innovation Challenges (auto-discovered 2026-10-07)</t>
+          <t>WEF UpLink Innovation Challenges (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -27688,7 +27688,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -27769,7 +27769,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -27850,7 +27850,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -27931,7 +27931,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -28012,7 +28012,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -28093,7 +28093,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -28174,7 +28174,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -28255,7 +28255,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -28336,7 +28336,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -28417,7 +28417,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -28498,7 +28498,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -28579,7 +28579,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -28660,7 +28660,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -28741,7 +28741,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -28822,7 +28822,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -28903,7 +28903,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28984,7 +28984,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -29065,7 +29065,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -29146,7 +29146,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -29227,7 +29227,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -29308,7 +29308,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29389,7 +29389,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29470,7 +29470,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29551,7 +29551,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29632,7 +29632,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29713,7 +29713,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29794,7 +29794,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -29875,7 +29875,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -29956,7 +29956,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30037,7 +30037,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30118,7 +30118,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30199,7 +30199,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -30280,7 +30280,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -30361,7 +30361,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -30442,7 +30442,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -30523,7 +30523,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -30685,7 +30685,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -30766,7 +30766,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -30847,7 +30847,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-07)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -30928,7 +30928,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -31009,7 +31009,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -31090,7 +31090,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -31171,7 +31171,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -31252,7 +31252,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -31333,7 +31333,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -31414,7 +31414,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -31495,7 +31495,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -31576,7 +31576,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -31657,7 +31657,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -31738,7 +31738,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -31819,7 +31819,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -31900,7 +31900,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -31981,7 +31981,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -32062,7 +32062,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -32143,7 +32143,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -32224,7 +32224,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -32305,7 +32305,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -32386,7 +32386,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -32467,7 +32467,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -32548,7 +32548,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -32629,7 +32629,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -32710,7 +32710,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -32791,7 +32791,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -32872,7 +32872,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -32953,7 +32953,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -33034,7 +33034,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -33115,7 +33115,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -33196,7 +33196,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -33277,7 +33277,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -33358,7 +33358,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -33439,7 +33439,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -33520,7 +33520,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -33601,7 +33601,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -33682,7 +33682,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -33763,7 +33763,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -33844,7 +33844,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -33925,7 +33925,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -34006,7 +34006,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -34087,7 +34087,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-07)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -34168,7 +34168,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -34249,7 +34249,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -34330,7 +34330,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -34411,7 +34411,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -34492,7 +34492,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -34573,7 +34573,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -34654,7 +34654,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -34735,7 +34735,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -34816,7 +34816,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -34897,7 +34897,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -34978,7 +34978,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -35059,7 +35059,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -35140,7 +35140,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -35221,7 +35221,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -35302,7 +35302,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -35383,7 +35383,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -35464,7 +35464,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -35545,7 +35545,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -35626,7 +35626,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -35707,7 +35707,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -35788,7 +35788,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -35869,7 +35869,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -35950,7 +35950,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -36031,7 +36031,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -36112,7 +36112,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -36193,7 +36193,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -36274,7 +36274,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -36355,7 +36355,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -36436,7 +36436,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -36517,7 +36517,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -36598,7 +36598,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -36679,7 +36679,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -36760,7 +36760,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -36841,7 +36841,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -36922,7 +36922,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -37003,7 +37003,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -37084,7 +37084,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -37165,7 +37165,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -37246,7 +37246,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -37327,7 +37327,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -37408,7 +37408,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -37489,7 +37489,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -37570,7 +37570,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -37651,7 +37651,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -37732,7 +37732,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -37813,7 +37813,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -37894,7 +37894,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -37975,7 +37975,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -38056,7 +38056,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -38137,7 +38137,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-07)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -38218,7 +38218,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -38299,7 +38299,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -38380,7 +38380,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -38461,7 +38461,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -38542,7 +38542,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -38623,7 +38623,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -38704,7 +38704,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -38785,7 +38785,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -38866,7 +38866,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -38947,7 +38947,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -39028,7 +39028,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -39109,7 +39109,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -39190,7 +39190,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -39271,7 +39271,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -39352,7 +39352,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -39433,7 +39433,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -39514,7 +39514,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -39595,7 +39595,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -39676,7 +39676,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -39757,7 +39757,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -39838,7 +39838,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -39919,7 +39919,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -40000,7 +40000,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -40081,7 +40081,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -40162,7 +40162,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -40243,7 +40243,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -40324,7 +40324,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -40405,7 +40405,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -40486,7 +40486,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -40567,7 +40567,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -40648,7 +40648,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -40729,7 +40729,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -40810,7 +40810,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-07)</t>
+          <t>Slush 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -40891,7 +40891,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -40972,7 +40972,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -41053,7 +41053,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -41134,7 +41134,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -41215,7 +41215,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -41296,7 +41296,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -41377,7 +41377,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -41458,7 +41458,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -41539,7 +41539,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -41620,7 +41620,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -41701,7 +41701,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -41782,7 +41782,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -41863,7 +41863,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -41944,7 +41944,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -42025,7 +42025,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -42106,7 +42106,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -42187,7 +42187,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -42268,7 +42268,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -42349,7 +42349,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -42430,7 +42430,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -42511,7 +42511,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -42592,7 +42592,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -42673,7 +42673,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -42754,7 +42754,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -42835,7 +42835,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -42916,7 +42916,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -42997,7 +42997,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -43078,7 +43078,7 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -43159,7 +43159,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -43240,7 +43240,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -43321,7 +43321,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G318" t="n">
@@ -43402,7 +43402,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -43483,7 +43483,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G320" t="n">
@@ -43564,7 +43564,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G321" t="n">
@@ -43645,7 +43645,7 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -43726,7 +43726,7 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G323" t="n">
@@ -43807,7 +43807,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G324" t="n">
@@ -43888,7 +43888,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G325" t="n">
@@ -43969,7 +43969,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G326" t="n">
@@ -44050,7 +44050,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-07)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G327" t="n">
@@ -44131,7 +44131,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-07)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G328" t="n">
@@ -44212,7 +44212,7 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-07)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G329" t="n">
@@ -44293,7 +44293,7 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-07)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G330" t="n">
@@ -44374,7 +44374,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-07)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G331" t="n">
@@ -44455,7 +44455,7 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-07)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G332" t="n">
@@ -44536,7 +44536,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-07)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G333" t="n">
@@ -44617,7 +44617,7 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-07)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G334" t="n">
@@ -44698,7 +44698,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-07)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G335" t="n">
@@ -44779,7 +44779,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-07)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G336" t="n">
@@ -44860,7 +44860,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-07)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G337" t="n">
@@ -44941,7 +44941,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-07)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G338" t="n">
@@ -45022,7 +45022,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G339" t="n">
@@ -45103,7 +45103,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G340" t="n">
@@ -45184,7 +45184,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G341" t="n">
@@ -45265,7 +45265,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G342" t="n">
@@ -45346,7 +45346,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G343" t="n">
@@ -45427,7 +45427,7 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G344" t="n">
@@ -45508,7 +45508,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G345" t="n">
@@ -45589,7 +45589,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G346" t="n">
@@ -45670,7 +45670,7 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G347" t="n">
@@ -45751,7 +45751,7 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G348" t="n">
@@ -45832,7 +45832,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G349" t="n">
@@ -45913,7 +45913,7 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G350" t="n">
@@ -45994,7 +45994,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G351" t="n">
@@ -46075,7 +46075,7 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G352" t="n">
@@ -46156,7 +46156,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G353" t="n">
@@ -46237,7 +46237,7 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G354" t="n">
@@ -46318,7 +46318,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G355" t="n">
@@ -46399,7 +46399,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G356" t="n">
@@ -46480,7 +46480,7 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G357" t="n">
@@ -46561,7 +46561,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G358" t="n">
@@ -46642,7 +46642,7 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G359" t="n">
@@ -46702,7 +46702,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>The TradFi-DeFi Market Map</t>
+          <t>State of AI Q3’26</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -46723,7 +46723,7 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G360" t="n">
@@ -46783,7 +46783,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>State of Venture Q3’26</t>
+          <t>The TradFi-DeFi Market Map</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -46804,7 +46804,7 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G361" t="n">
@@ -46885,7 +46885,7 @@
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-07)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G362" t="n">
@@ -46966,7 +46966,7 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G363" t="n">
@@ -47047,7 +47047,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G364" t="n">
@@ -47128,7 +47128,7 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G365" t="n">
@@ -47209,7 +47209,7 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G366" t="n">
@@ -47290,7 +47290,7 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G367" t="n">
@@ -47371,7 +47371,7 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G368" t="n">
@@ -47452,7 +47452,7 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G369" t="n">
@@ -47533,7 +47533,7 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G370" t="n">
@@ -47614,7 +47614,7 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G371" t="n">
@@ -47695,7 +47695,7 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G372" t="n">
@@ -47776,7 +47776,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G373" t="n">
@@ -47857,7 +47857,7 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G374" t="n">
@@ -47938,7 +47938,7 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G375" t="n">
@@ -48019,7 +48019,7 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G376" t="n">
@@ -48100,7 +48100,7 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G377" t="n">
@@ -48181,7 +48181,7 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G378" t="n">
@@ -48262,7 +48262,7 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G379" t="n">
@@ -48343,7 +48343,7 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G380" t="n">
@@ -48424,7 +48424,7 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G381" t="n">
@@ -48505,7 +48505,7 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G382" t="n">
@@ -48586,7 +48586,7 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G383" t="n">
@@ -48667,7 +48667,7 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G384" t="n">
@@ -48748,7 +48748,7 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G385" t="n">
@@ -48829,7 +48829,7 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G386" t="n">
@@ -48910,7 +48910,7 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G387" t="n">
@@ -48991,7 +48991,7 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G388" t="n">
@@ -49072,7 +49072,7 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G389" t="n">
@@ -49153,7 +49153,7 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-07)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
         </is>
       </c>
       <c r="G390" t="n">
@@ -49274,7 +49274,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-07T04:19:23.776138+00:00</t>
+          <t>2026-10-12T22:27:14.987352+00:00</t>
         </is>
       </c>
     </row>
@@ -49301,7 +49301,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-07T04:19:31.509450+00:00</t>
+          <t>2026-10-12T22:27:22.512101+00:00</t>
         </is>
       </c>
     </row>
@@ -49328,7 +49328,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-07T04:19:53.642419+00:00</t>
+          <t>2026-10-12T22:27:44.342069+00:00</t>
         </is>
       </c>
     </row>
@@ -49355,7 +49355,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-07T04:20:02.831543+00:00</t>
+          <t>2026-10-12T22:28:12.973842+00:00</t>
         </is>
       </c>
     </row>
@@ -49382,7 +49382,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-07T04:20:07.987449+00:00</t>
+          <t>2026-10-12T22:28:18.049935+00:00</t>
         </is>
       </c>
     </row>
@@ -49409,7 +49409,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-07T04:20:09.322538+00:00</t>
+          <t>2026-10-12T22:28:19.486142+00:00</t>
         </is>
       </c>
     </row>
@@ -49436,7 +49436,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-07T04:20:09.617384+00:00</t>
+          <t>2026-10-12T22:28:19.595145+00:00</t>
         </is>
       </c>
     </row>
@@ -49463,7 +49463,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-07T04:20:09.891033+00:00</t>
+          <t>2026-10-12T22:28:19.839507+00:00</t>
         </is>
       </c>
     </row>
@@ -49490,7 +49490,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-07T04:20:13.871552+00:00</t>
+          <t>2026-10-12T22:28:24.003314+00:00</t>
         </is>
       </c>
     </row>
@@ -49520,7 +49520,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-07T04:20:18.437976+00:00</t>
+          <t>2026-10-12T22:28:28.489164+00:00</t>
         </is>
       </c>
     </row>
@@ -49547,7 +49547,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-07T04:20:48.953417+00:00</t>
+          <t>2026-10-12T22:28:58.997998+00:00</t>
         </is>
       </c>
     </row>
@@ -49577,7 +49577,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-07T04:21:03.498171+00:00</t>
+          <t>2026-10-12T22:29:08.628347+00:00</t>
         </is>
       </c>
     </row>
@@ -49604,7 +49604,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-07T04:21:33.979882+00:00</t>
+          <t>2026-10-12T22:29:39.118805+00:00</t>
         </is>
       </c>
     </row>
@@ -49631,7 +49631,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-07T04:21:38.353846+00:00</t>
+          <t>2026-10-12T22:29:43.538441+00:00</t>
         </is>
       </c>
     </row>
@@ -49661,7 +49661,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-07T04:21:41.669294+00:00</t>
+          <t>2026-10-12T22:29:47.107204+00:00</t>
         </is>
       </c>
     </row>
@@ -49691,7 +49691,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-07T04:22:12.198786+00:00</t>
+          <t>2026-10-12T22:30:17.644096+00:00</t>
         </is>
       </c>
     </row>
@@ -49718,7 +49718,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-07T04:22:42.835098+00:00</t>
+          <t>2026-10-12T22:30:48.331379+00:00</t>
         </is>
       </c>
     </row>
@@ -49745,7 +49745,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-07T04:22:45.759265+00:00</t>
+          <t>2026-10-12T22:30:51.311548+00:00</t>
         </is>
       </c>
     </row>
@@ -49775,7 +49775,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-07T04:22:53.328123+00:00</t>
+          <t>2026-10-12T22:30:58.160486+00:00</t>
         </is>
       </c>
     </row>
@@ -49802,7 +49802,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-07T04:23:23.814536+00:00</t>
+          <t>2026-10-12T22:31:28.648677+00:00</t>
         </is>
       </c>
     </row>
@@ -49829,7 +49829,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-07T04:23:27.771260+00:00</t>
+          <t>2026-10-12T22:31:32.545927+00:00</t>
         </is>
       </c>
     </row>

--- a/reports/Pioneer_Innovator_Sources_AUTO.xlsx
+++ b/reports/Pioneer_Innovator_Sources_AUTO.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J390"/>
+  <dimension ref="A1:J399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -504,7 +504,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -680,7 +680,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -812,7 +812,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1516,7 +1516,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1912,7 +1912,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2088,7 +2088,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2264,7 +2264,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2352,7 +2352,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2528,7 +2528,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2660,7 +2660,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2792,7 +2792,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3144,7 +3144,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3276,7 +3276,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3408,7 +3408,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3540,7 +3540,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3628,7 +3628,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -3892,7 +3892,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -3980,7 +3980,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4156,7 +4156,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4200,7 +4200,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4244,7 +4244,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4288,7 +4288,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4508,7 +4508,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4552,7 +4552,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4640,7 +4640,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4684,7 +4684,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4728,7 +4728,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -4860,7 +4860,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -4948,7 +4948,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -4992,7 +4992,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5168,7 +5168,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5300,7 +5300,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5432,7 +5432,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5564,7 +5564,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5608,7 +5608,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5652,7 +5652,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>WEF UpLink Innovation Challenges (auto-discovered 2026-10-12)</t>
+          <t>WEF UpLink Innovation Challenges (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>WEF UpLink Innovation Challenges (auto-discovered 2026-10-12)</t>
+          <t>WEF UpLink Innovation Challenges (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -5872,7 +5872,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>WEF UpLink Innovation Challenges (auto-discovered 2026-10-12)</t>
+          <t>WEF UpLink Innovation Challenges (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -5960,7 +5960,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6004,7 +6004,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6092,7 +6092,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6136,7 +6136,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6400,7 +6400,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6444,7 +6444,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6532,7 +6532,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -6708,7 +6708,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -6884,7 +6884,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -6928,7 +6928,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -7060,7 +7060,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7104,7 +7104,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -7148,7 +7148,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -7192,7 +7192,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -7368,7 +7368,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -7500,7 +7500,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -7588,7 +7588,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -7720,7 +7720,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -7808,7 +7808,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -7940,7 +7940,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -8072,7 +8072,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -8116,7 +8116,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -8160,7 +8160,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -8292,7 +8292,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -8380,7 +8380,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -8424,7 +8424,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -8600,7 +8600,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -8732,7 +8732,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -8820,7 +8820,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -8908,7 +8908,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -8952,7 +8952,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -8996,7 +8996,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -9040,7 +9040,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -9216,7 +9216,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -9392,7 +9392,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -9436,7 +9436,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -9568,7 +9568,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -9656,7 +9656,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -9788,7 +9788,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -9832,7 +9832,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -9920,7 +9920,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -10052,7 +10052,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -10184,7 +10184,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -10272,7 +10272,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -10316,7 +10316,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -10404,7 +10404,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -10448,7 +10448,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -10536,7 +10536,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -10580,7 +10580,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -10624,7 +10624,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -10668,7 +10668,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -10712,7 +10712,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -10756,7 +10756,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -10932,7 +10932,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -11020,7 +11020,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -11064,7 +11064,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -11108,7 +11108,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -11152,7 +11152,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -11196,7 +11196,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -11240,7 +11240,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -11328,7 +11328,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -11372,7 +11372,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -11416,7 +11416,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -11460,7 +11460,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -11504,7 +11504,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -11592,7 +11592,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -11636,7 +11636,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -11680,7 +11680,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -11724,7 +11724,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -11768,7 +11768,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -11812,7 +11812,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -11856,7 +11856,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -11900,7 +11900,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -11944,7 +11944,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -11988,7 +11988,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -12032,7 +12032,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -12208,7 +12208,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -12252,7 +12252,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -12296,7 +12296,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -12340,7 +12340,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -12384,7 +12384,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -12428,7 +12428,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -12472,7 +12472,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -12516,7 +12516,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -12604,7 +12604,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -12648,7 +12648,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -12692,7 +12692,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -12780,7 +12780,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -12868,7 +12868,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -12912,7 +12912,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -12956,7 +12956,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -13000,7 +13000,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -13044,7 +13044,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -13067,7 +13067,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>The World’s Largest Startup and Investor Connector Event</t>
+          <t>Expand North Star</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -13088,7 +13088,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -13111,7 +13111,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>WHAT’S NEW IN 2026</t>
+          <t>GITEX GLOBAL</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -13132,7 +13132,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -13155,7 +13155,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>ENS FOUNDERS ACADEMY</t>
+          <t>WHAT’S NEW IN 2026</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>NS PLAY</t>
+          <t>THE FOUNDER’S PASS</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -13220,7 +13220,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -13243,7 +13243,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>DIGIHEALTH–BIOTECH</t>
+          <t>SUPERNOVA 0X</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -13264,7 +13264,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -13287,7 +13287,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>ENS26 Backers Pitch</t>
+          <t>NO FINALS</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13308,7 +13308,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -13331,7 +13331,7 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Be where the smart money moves — only at Expand North Star</t>
+          <t>Save Your Wardrobe</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -13352,7 +13352,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -13375,7 +13375,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>THE FOUNDER’S PASS</t>
+          <t>A ‘turning point’ at ENS</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -13396,7 +13396,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -13419,7 +13419,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>FOUNDER RESTRUCTURE</t>
+          <t>BYTRIX Technologies</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -13440,7 +13440,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -13463,7 +13463,7 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>COMMERCIAL DEEPTECH</t>
+          <t>How BYTRIX turned conversations into six-figure deals</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -13484,7 +13484,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -13507,7 +13507,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Gilberto Silva</t>
+          <t>Laplace</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -13528,7 +13528,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -13551,7 +13551,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>H.E. Alia Abdulla Al Mazrouei</t>
+          <t>From Pitch to $900M+ in Tokenisation Deals</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -13595,7 +13595,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>H.E. Faisal Al Bannai</t>
+          <t>SatLeo Labs</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -13639,7 +13639,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Dr. Christian Weedbrook</t>
+          <t>What happened in just 10 minutes?</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -13660,7 +13660,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -13683,7 +13683,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Dr. Dennis Hong</t>
+          <t>MIstikist</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -13704,7 +13704,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -13727,7 +13727,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Jason Derulo</t>
+          <t>NovaPilot</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -13748,7 +13748,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -13771,7 +13771,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Manu Chopra</t>
+          <t>Lunar Limited</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -13792,7 +13792,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -13815,7 +13815,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Neil Patel</t>
+          <t>NORTH STAR BY NIGHT</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -13836,7 +13836,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -13859,7 +13859,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Peng Xiao</t>
+          <t>GITEX TECHCATION</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -13880,7 +13880,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -13903,7 +13903,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Prashanth Prakash</t>
+          <t>TechCation</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -13924,7 +13924,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -13947,7 +13947,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Randi Zuckerberg</t>
+          <t>THE GITEX Summit</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -13968,7 +13968,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Sean Garnier</t>
+          <t>TECH LEADERS</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -14012,7 +14012,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -14035,7 +14035,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Sean o'Sullivan</t>
+          <t>Gilberto Silva</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Tej Lalvani</t>
+          <t>H.E. Alia Abdulla Al Mazrouei</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -14100,7 +14100,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -14123,7 +14123,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Vijay Shekhar Sharma</t>
+          <t>Jason Derulo</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -14144,7 +14144,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -14167,7 +14167,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Dr. Guy Diedrich</t>
+          <t>Neil Patel</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -14188,7 +14188,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -14211,7 +14211,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>H.E. Omar Sultan Alolama</t>
+          <t>Peng Xiao</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -14232,7 +14232,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -14255,7 +14255,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>A.R. Rahman</t>
+          <t>Sean o'Sullivan</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -14276,7 +14276,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -14299,7 +14299,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>David Cohen</t>
+          <t>H.E. Omar Sultan Alolama</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -14320,7 +14320,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -14343,7 +14343,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Deep Nishar</t>
+          <t>Christian Weedbrook</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -14387,7 +14387,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Deepinder Goyal</t>
+          <t>Greg Jackson</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -14408,7 +14408,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -14431,7 +14431,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Dr. Ghita Mezzour</t>
+          <t>Sir Martin Sorrell</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -14452,7 +14452,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -14475,7 +14475,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Greg Jackson</t>
+          <t>Vinod Khosla</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -14496,7 +14496,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -14519,7 +14519,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Dr. Mactar Seck</t>
+          <t>EMIL SYUNDYUKOV</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -14540,7 +14540,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -14563,7 +14563,7 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>H.E. Hamad Almansoori</t>
+          <t>MAYANK YADAV</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -14607,7 +14607,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>H.E. Ms. Mariam Al Mheiri</t>
+          <t>DAVID COHEN</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -14628,7 +14628,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -14651,7 +14651,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Jack Selby</t>
+          <t>ZHONG XU</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -14672,7 +14672,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -14695,7 +14695,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Sir Martin Sorrell</t>
+          <t>NAKUL GARG</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -14716,7 +14716,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -14739,7 +14739,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Sir Tim Berners Lee</t>
+          <t>JANADE DU PLESSIS</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -14760,7 +14760,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -14783,7 +14783,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Vinod Khosla</t>
+          <t>GEOFFREY COSTILHES</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
@@ -14804,7 +14804,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -14848,7 +14848,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -14892,7 +14892,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -14936,7 +14936,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -14980,7 +14980,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -15024,7 +15024,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -15068,7 +15068,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -15112,7 +15112,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -15156,7 +15156,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -15200,7 +15200,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -15244,7 +15244,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -15288,7 +15288,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -15332,7 +15332,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -15420,7 +15420,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -15464,7 +15464,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -15508,7 +15508,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -15552,7 +15552,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -15596,7 +15596,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -15640,7 +15640,7 @@
       </c>
       <c r="H346" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I346" t="inlineStr">
@@ -15684,7 +15684,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -15728,7 +15728,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -15772,7 +15772,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -15816,7 +15816,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -15860,7 +15860,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -15948,7 +15948,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -15992,7 +15992,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -16036,7 +16036,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -16080,7 +16080,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -16124,7 +16124,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -16168,7 +16168,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -16212,7 +16212,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -16235,7 +16235,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>State of AI Q3’26</t>
+          <t>CEO Interview: Vitazi.ai</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -16256,7 +16256,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -16279,7 +16279,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>The TradFi-DeFi Market Map</t>
+          <t>You might also like</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -16300,7 +16300,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -16323,7 +16323,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>You might also like</t>
+          <t>Accelerator Programme</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -16339,17 +16339,17 @@
       <c r="F362" t="inlineStr"/>
       <c r="G362" t="inlineStr">
         <is>
-          <t>Editorial List</t>
+          <t>Gov/IGO Program</t>
         </is>
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>NATO DIANA Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
         <is>
-          <t>Auto-discovered via agentic source scan of CB Insights AI 100. UNVERIFIED — confirm entity identity and current status before acting on this row.</t>
+          <t>Auto-discovered via agentic source scan of NATO DIANA Innovators. UNVERIFIED — confirm entity identity and current status before acting on this row.</t>
         </is>
       </c>
       <c r="J362" t="inlineStr">
@@ -16367,7 +16367,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>What is the EIC Accelerator ?</t>
+          <t>Challenges</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -16388,12 +16388,12 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>NATO DIANA Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
         <is>
-          <t>Auto-discovered via agentic source scan of EU EIC Accelerator Companies. UNVERIFIED — confirm entity identity and current status before acting on this row.</t>
+          <t>Auto-discovered via agentic source scan of NATO DIANA Innovators. UNVERIFIED — confirm entity identity and current status before acting on this row.</t>
         </is>
       </c>
       <c r="J363" t="inlineStr">
@@ -16411,7 +16411,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>EIC Accelerator</t>
+          <t>Test centres</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -16432,12 +16432,12 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>NATO DIANA Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
         <is>
-          <t>Auto-discovered via agentic source scan of EU EIC Accelerator Companies. UNVERIFIED — confirm entity identity and current status before acting on this row.</t>
+          <t>Auto-discovered via agentic source scan of NATO DIANA Innovators. UNVERIFIED — confirm entity identity and current status before acting on this row.</t>
         </is>
       </c>
       <c r="J364" t="inlineStr">
@@ -16455,7 +16455,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Grant only</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -16476,12 +16476,12 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>NATO DIANA Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
         <is>
-          <t>Auto-discovered via agentic source scan of EU EIC Accelerator Companies. UNVERIFIED — confirm entity identity and current status before acting on this row.</t>
+          <t>Auto-discovered via agentic source scan of NATO DIANA Innovators. UNVERIFIED — confirm entity identity and current status before acting on this row.</t>
         </is>
       </c>
       <c r="J365" t="inlineStr">
@@ -16499,7 +16499,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Blended finance:</t>
+          <t>Capital Network</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -16520,12 +16520,12 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>NATO DIANA Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
         <is>
-          <t>Auto-discovered via agentic source scan of EU EIC Accelerator Companies. UNVERIFIED — confirm entity identity and current status before acting on this row.</t>
+          <t>Auto-discovered via agentic source scan of NATO DIANA Innovators. UNVERIFIED — confirm entity identity and current status before acting on this row.</t>
         </is>
       </c>
       <c r="J366" t="inlineStr">
@@ -16543,7 +16543,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>Investment only:</t>
+          <t>Join our team</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -16564,12 +16564,12 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>NATO DIANA Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>Auto-discovered via agentic source scan of EU EIC Accelerator Companies. UNVERIFIED — confirm entity identity and current status before acting on this row.</t>
+          <t>Auto-discovered via agentic source scan of NATO DIANA Innovators. UNVERIFIED — confirm entity identity and current status before acting on this row.</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
@@ -16587,7 +16587,7 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Access to global partners</t>
+          <t>News</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -16608,12 +16608,12 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>NATO DIANA Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
         <is>
-          <t>Auto-discovered via agentic source scan of EU EIC Accelerator Companies. UNVERIFIED — confirm entity identity and current status before acting on this row.</t>
+          <t>Auto-discovered via agentic source scan of NATO DIANA Innovators. UNVERIFIED — confirm entity identity and current status before acting on this row.</t>
         </is>
       </c>
       <c r="J368" t="inlineStr">
@@ -16631,7 +16631,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Access to coaches, mentors, expertise and training</t>
+          <t>Content &amp; Social</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -16652,12 +16652,12 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>NATO DIANA Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
         <is>
-          <t>Auto-discovered via agentic source scan of EU EIC Accelerator Companies. UNVERIFIED — confirm entity identity and current status before acting on this row.</t>
+          <t>Auto-discovered via agentic source scan of NATO DIANA Innovators. UNVERIFIED — confirm entity identity and current status before acting on this row.</t>
         </is>
       </c>
       <c r="J369" t="inlineStr">
@@ -16675,7 +16675,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Access to innovation ecosystem and peers</t>
+          <t>What is the EIC Accelerator ?</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -16696,7 +16696,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -16719,7 +16719,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Writing a short proposal</t>
+          <t>EIC Accelerator</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -16740,7 +16740,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -16763,7 +16763,7 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Submission of a full proposal</t>
+          <t>Grant only</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -16784,7 +16784,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -16807,7 +16807,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Face to face interview with the EIC Jury</t>
+          <t>Blended finance:</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -16828,7 +16828,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -16851,7 +16851,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>EIC Jury</t>
+          <t>Investment only:</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -16872,7 +16872,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -16895,7 +16895,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>General publications</t>
+          <t>Access to global partners</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -16916,7 +16916,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -16939,7 +16939,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Who can apply?</t>
+          <t>Access to coaches, mentors, expertise and training</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -16960,7 +16960,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -16983,7 +16983,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Single start-up or SME (including spin-outs)</t>
+          <t>Access to innovation ecosystem and peers</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -17004,7 +17004,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -17027,7 +17027,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Applicants from third countries:</t>
+          <t>Writing a short proposal</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -17048,7 +17048,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -17071,7 +17071,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Concurrent applications:</t>
+          <t>Submission of a full proposal</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
@@ -17092,7 +17092,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -17115,7 +17115,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>A pitch-deck of up to ten slides in PDF format;</t>
+          <t>Face to face interview with the EIC Jury</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -17136,7 +17136,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -17159,7 +17159,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Grant only:</t>
+          <t>EIC Jury</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -17180,7 +17180,7 @@
       </c>
       <c r="H381" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I381" t="inlineStr">
@@ -17203,7 +17203,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>General information</t>
+          <t>General publications</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -17224,7 +17224,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -17247,7 +17247,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Direct submissions</t>
+          <t>Who can apply?</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
@@ -17268,7 +17268,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -17291,7 +17291,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Fast Track</t>
+          <t>Single start-up or SME (including spin-outs)</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -17312,7 +17312,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -17335,7 +17335,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Plug-In</t>
+          <t>Applicants from third countries:</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -17356,7 +17356,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -17379,7 +17379,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Do you need help ?</t>
+          <t>Concurrent applications:</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -17400,7 +17400,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -17423,7 +17423,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>A pitch-deck of up to ten slides in PDF format;</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -17467,7 +17467,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>News article</t>
+          <t>Grant only:</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -17488,7 +17488,7 @@
       </c>
       <c r="H388" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I388" t="inlineStr">
@@ -17511,7 +17511,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>General information</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -17532,7 +17532,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -17555,7 +17555,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Direct submissions</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
@@ -17576,7 +17576,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -17585,6 +17585,402 @@
         </is>
       </c>
       <c r="J390" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr"/>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Fast Track</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr"/>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>Gov/IGO Program</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>Auto-discovered via agentic source scan of EU EIC Accelerator Companies. UNVERIFIED — confirm entity identity and current status before acting on this row.</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr"/>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Plug-In</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr"/>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>Gov/IGO Program</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>Auto-discovered via agentic source scan of EU EIC Accelerator Companies. UNVERIFIED — confirm entity identity and current status before acting on this row.</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr"/>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Do you need help ?</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr"/>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>Gov/IGO Program</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>Auto-discovered via agentic source scan of EU EIC Accelerator Companies. UNVERIFIED — confirm entity identity and current status before acting on this row.</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr"/>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr"/>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>Gov/IGO Program</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>Auto-discovered via agentic source scan of EU EIC Accelerator Companies. UNVERIFIED — confirm entity identity and current status before acting on this row.</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr"/>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>News article</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr"/>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>Gov/IGO Program</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>Auto-discovered via agentic source scan of EU EIC Accelerator Companies. UNVERIFIED — confirm entity identity and current status before acting on this row.</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr"/>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr"/>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>Gov/IGO Program</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>Auto-discovered via agentic source scan of EU EIC Accelerator Companies. UNVERIFIED — confirm entity identity and current status before acting on this row.</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr"/>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Online only</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr"/>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>Gov/IGO Program</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>Auto-discovered via agentic source scan of EU EIC Accelerator Companies. UNVERIFIED — confirm entity identity and current status before acting on this row.</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr"/>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr"/>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>Gov/IGO Program</t>
+        </is>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>Auto-discovered via agentic source scan of EU EIC Accelerator Companies. UNVERIFIED — confirm entity identity and current status before acting on this row.</t>
+        </is>
+      </c>
+      <c r="J398" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr"/>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr"/>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>Gov/IGO Program</t>
+        </is>
+      </c>
+      <c r="H399" t="inlineStr">
+        <is>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
+        </is>
+      </c>
+      <c r="I399" t="inlineStr">
+        <is>
+          <t>Auto-discovered via agentic source scan of EU EIC Accelerator Companies. UNVERIFIED — confirm entity identity and current status before acting on this row.</t>
+        </is>
+      </c>
+      <c r="J399" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -17601,7 +17997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S390"/>
+  <dimension ref="A1:S399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17725,7 +18121,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -17806,7 +18202,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -17887,7 +18283,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -17968,7 +18364,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -18049,7 +18445,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -18130,7 +18526,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -18211,7 +18607,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -18292,7 +18688,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -18373,7 +18769,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -18454,7 +18850,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -18535,7 +18931,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -18616,7 +19012,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -18697,7 +19093,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -18778,7 +19174,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -18859,7 +19255,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -18940,7 +19336,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -19021,7 +19417,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -19102,7 +19498,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -19183,7 +19579,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -19264,7 +19660,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -19345,7 +19741,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -19426,7 +19822,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -19507,7 +19903,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -19588,7 +19984,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -19669,7 +20065,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -19750,7 +20146,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -19831,7 +20227,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -19912,7 +20308,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -19993,7 +20389,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -20074,7 +20470,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -20155,7 +20551,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -20236,7 +20632,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -20317,7 +20713,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -20398,7 +20794,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -20479,7 +20875,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -20560,7 +20956,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -20641,7 +21037,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -20722,7 +21118,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -20803,7 +21199,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -20884,7 +21280,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>WEF Technology Pioneers (auto-discovered 2026-10-12)</t>
+          <t>WEF Technology Pioneers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -20965,7 +21361,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -21046,7 +21442,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -21127,7 +21523,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -21208,7 +21604,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -21289,7 +21685,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -21370,7 +21766,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -21451,7 +21847,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -21532,7 +21928,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -21613,7 +22009,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -21694,7 +22090,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -21775,7 +22171,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -21856,7 +22252,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -21937,7 +22333,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -22018,7 +22414,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -22099,7 +22495,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -22180,7 +22576,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -22261,7 +22657,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -22342,7 +22738,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -22423,7 +22819,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -22504,7 +22900,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -22585,7 +22981,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -22666,7 +23062,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -22747,7 +23143,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -22828,7 +23224,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -22909,7 +23305,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -22990,7 +23386,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -23071,7 +23467,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -23152,7 +23548,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -23233,7 +23629,7 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -23314,7 +23710,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -23395,7 +23791,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -23476,7 +23872,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -23557,7 +23953,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -23638,7 +24034,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -23719,7 +24115,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -23800,7 +24196,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -23881,7 +24277,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -23962,7 +24358,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -24043,7 +24439,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -24124,7 +24520,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>WEF Global Innovators (auto-discovered 2026-10-12)</t>
+          <t>WEF Global Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -24205,7 +24601,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -24286,7 +24682,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -24367,7 +24763,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -24448,7 +24844,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -24529,7 +24925,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -24610,7 +25006,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -24691,7 +25087,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -24772,7 +25168,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -24853,7 +25249,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -24934,7 +25330,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -25015,7 +25411,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -25096,7 +25492,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -25177,7 +25573,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -25258,7 +25654,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -25339,7 +25735,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -25420,7 +25816,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -25501,7 +25897,7 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -25582,7 +25978,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -25663,7 +26059,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -25744,7 +26140,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -25825,7 +26221,7 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -25906,7 +26302,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -25987,7 +26383,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -26068,7 +26464,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -26149,7 +26545,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -26230,7 +26626,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -26311,7 +26707,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -26392,7 +26788,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -26473,7 +26869,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -26554,7 +26950,7 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -26635,7 +27031,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -26716,7 +27112,7 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -26797,7 +27193,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -26878,7 +27274,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -26959,7 +27355,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -27040,7 +27436,7 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -27121,7 +27517,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -27202,7 +27598,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -27283,7 +27679,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -27364,7 +27760,7 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>WEF Unicorns Community (auto-discovered 2026-10-12)</t>
+          <t>WEF Unicorns Community (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -27445,7 +27841,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>WEF UpLink Innovation Challenges (auto-discovered 2026-10-12)</t>
+          <t>WEF UpLink Innovation Challenges (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -27526,7 +27922,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>WEF UpLink Innovation Challenges (auto-discovered 2026-10-12)</t>
+          <t>WEF UpLink Innovation Challenges (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -27607,7 +28003,7 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>WEF UpLink Innovation Challenges (auto-discovered 2026-10-12)</t>
+          <t>WEF UpLink Innovation Challenges (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -27688,7 +28084,7 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -27769,7 +28165,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -27850,7 +28246,7 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -27931,7 +28327,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -28012,7 +28408,7 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -28093,7 +28489,7 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -28174,7 +28570,7 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -28255,7 +28651,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -28336,7 +28732,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -28417,7 +28813,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -28498,7 +28894,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -28579,7 +28975,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -28660,7 +29056,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -28741,7 +29137,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -28822,7 +29218,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -28903,7 +29299,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -28984,7 +29380,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -29065,7 +29461,7 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -29146,7 +29542,7 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G143" t="n">
@@ -29227,7 +29623,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -29308,7 +29704,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -29389,7 +29785,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -29470,7 +29866,7 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -29551,7 +29947,7 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -29632,7 +30028,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -29713,7 +30109,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -29794,7 +30190,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -29875,7 +30271,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -29956,7 +30352,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -30037,7 +30433,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -30118,7 +30514,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -30199,7 +30595,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -30280,7 +30676,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -30361,7 +30757,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -30442,7 +30838,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -30523,7 +30919,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -30604,7 +31000,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -30685,7 +31081,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -30766,7 +31162,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -30847,7 +31243,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-12)</t>
+          <t>UN ITU WSIS Prizes (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -30928,7 +31324,7 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -31009,7 +31405,7 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -31090,7 +31486,7 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -31171,7 +31567,7 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -31252,7 +31648,7 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -31333,7 +31729,7 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -31414,7 +31810,7 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -31495,7 +31891,7 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -31576,7 +31972,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -31657,7 +32053,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -31738,7 +32134,7 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -31819,7 +32215,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -31900,7 +32296,7 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -31981,7 +32377,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -32062,7 +32458,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -32143,7 +32539,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -32224,7 +32620,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -32305,7 +32701,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -32386,7 +32782,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -32467,7 +32863,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -32548,7 +32944,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -32629,7 +33025,7 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -32710,7 +33106,7 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -32791,7 +33187,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -32872,7 +33268,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -32953,7 +33349,7 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -33034,7 +33430,7 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -33115,7 +33511,7 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -33196,7 +33592,7 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -33277,7 +33673,7 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -33358,7 +33754,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -33439,7 +33835,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -33520,7 +33916,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -33601,7 +33997,7 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -33682,7 +34078,7 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -33763,7 +34159,7 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -33844,7 +34240,7 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -33925,7 +34321,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -34006,7 +34402,7 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -34087,7 +34483,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-12)</t>
+          <t>World Bank GovTech Innovation Challenge Awards (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G204" t="n">
@@ -34168,7 +34564,7 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -34249,7 +34645,7 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -34330,7 +34726,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -34411,7 +34807,7 @@
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -34492,7 +34888,7 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -34573,7 +34969,7 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -34654,7 +35050,7 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -34735,7 +35131,7 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -34816,7 +35212,7 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -34897,7 +35293,7 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -34978,7 +35374,7 @@
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -35059,7 +35455,7 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -35140,7 +35536,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -35221,7 +35617,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -35302,7 +35698,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -35383,7 +35779,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -35464,7 +35860,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -35545,7 +35941,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -35626,7 +36022,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -35707,7 +36103,7 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -35788,7 +36184,7 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -35869,7 +36265,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -35950,7 +36346,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -36031,7 +36427,7 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -36112,7 +36508,7 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -36193,7 +36589,7 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -36274,7 +36670,7 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -36355,7 +36751,7 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -36436,7 +36832,7 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -36517,7 +36913,7 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Global Entrepreneurs / Outliers (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -36598,7 +36994,7 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -36679,7 +37075,7 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -36760,7 +37156,7 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -36841,7 +37237,7 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -36922,7 +37318,7 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -37003,7 +37399,7 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -37084,7 +37480,7 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -37165,7 +37561,7 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -37246,7 +37642,7 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -37327,7 +37723,7 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G244" t="n">
@@ -37408,7 +37804,7 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -37489,7 +37885,7 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -37570,7 +37966,7 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -37651,7 +38047,7 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -37732,7 +38128,7 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -37813,7 +38209,7 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -37894,7 +38290,7 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -37975,7 +38371,7 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -38056,7 +38452,7 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -38137,7 +38533,7 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-12)</t>
+          <t>Endeavor Entrepreneur Companies Portfolio (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -38218,7 +38614,7 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -38299,7 +38695,7 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -38380,7 +38776,7 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -38461,7 +38857,7 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -38542,7 +38938,7 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -38623,7 +39019,7 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -38704,7 +39100,7 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -38785,7 +39181,7 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -38866,7 +39262,7 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G263" t="n">
@@ -38947,7 +39343,7 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -39028,7 +39424,7 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -39109,7 +39505,7 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G266" t="n">
@@ -39190,7 +39586,7 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -39271,7 +39667,7 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -39352,7 +39748,7 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -39433,7 +39829,7 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -39514,7 +39910,7 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -39595,7 +39991,7 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -39676,7 +40072,7 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G273" t="n">
@@ -39757,7 +40153,7 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -39838,7 +40234,7 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -39919,7 +40315,7 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G276" t="n">
@@ -40000,7 +40396,7 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -40081,7 +40477,7 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -40162,7 +40558,7 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -40243,7 +40639,7 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -40324,7 +40720,7 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G281" t="n">
@@ -40405,7 +40801,7 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -40486,7 +40882,7 @@
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -40567,7 +40963,7 @@
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -40648,7 +41044,7 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -40729,7 +41125,7 @@
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -40810,7 +41206,7 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Slush 100 (auto-discovered 2026-10-12)</t>
+          <t>Slush 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -40870,7 +41266,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>The World’s Largest Startup and Investor Connector Event</t>
+          <t>Expand North Star</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -40891,7 +41287,7 @@
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -40951,7 +41347,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>WHAT’S NEW IN 2026</t>
+          <t>GITEX GLOBAL</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -40972,7 +41368,7 @@
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -41032,7 +41428,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>ENS FOUNDERS ACADEMY</t>
+          <t>WHAT’S NEW IN 2026</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -41053,7 +41449,7 @@
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -41113,7 +41509,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>NS PLAY</t>
+          <t>THE FOUNDER’S PASS</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -41134,7 +41530,7 @@
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -41194,7 +41590,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>DIGIHEALTH–BIOTECH</t>
+          <t>SUPERNOVA 0X</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -41215,7 +41611,7 @@
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -41275,7 +41671,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>ENS26 Backers Pitch</t>
+          <t>NO FINALS</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -41296,7 +41692,7 @@
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -41356,7 +41752,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Be where the smart money moves — only at Expand North Star</t>
+          <t>Save Your Wardrobe</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -41377,7 +41773,7 @@
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -41437,7 +41833,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>THE FOUNDER’S PASS</t>
+          <t>A ‘turning point’ at ENS</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -41458,7 +41854,7 @@
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -41518,7 +41914,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>FOUNDER RESTRUCTURE</t>
+          <t>BYTRIX Technologies</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -41539,7 +41935,7 @@
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -41599,7 +41995,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>COMMERCIAL DEEPTECH</t>
+          <t>How BYTRIX turned conversations into six-figure deals</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -41620,7 +42016,7 @@
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G297" t="n">
@@ -41680,7 +42076,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Gilberto Silva</t>
+          <t>Laplace</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -41701,7 +42097,7 @@
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G298" t="n">
@@ -41761,7 +42157,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>H.E. Alia Abdulla Al Mazrouei</t>
+          <t>From Pitch to $900M+ in Tokenisation Deals</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -41782,7 +42178,7 @@
       </c>
       <c r="F299" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G299" t="n">
@@ -41842,7 +42238,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>H.E. Faisal Al Bannai</t>
+          <t>SatLeo Labs</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -41863,7 +42259,7 @@
       </c>
       <c r="F300" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G300" t="n">
@@ -41923,7 +42319,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Dr. Christian Weedbrook</t>
+          <t>What happened in just 10 minutes?</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -41944,7 +42340,7 @@
       </c>
       <c r="F301" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G301" t="n">
@@ -42004,7 +42400,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Dr. Dennis Hong</t>
+          <t>MIstikist</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -42025,7 +42421,7 @@
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -42085,7 +42481,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Jason Derulo</t>
+          <t>NovaPilot</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -42106,7 +42502,7 @@
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -42166,7 +42562,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Manu Chopra</t>
+          <t>Lunar Limited</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -42187,7 +42583,7 @@
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -42247,7 +42643,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Neil Patel</t>
+          <t>NORTH STAR BY NIGHT</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -42268,7 +42664,7 @@
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -42328,7 +42724,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Peng Xiao</t>
+          <t>GITEX TECHCATION</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -42349,7 +42745,7 @@
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -42409,7 +42805,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Prashanth Prakash</t>
+          <t>TechCation</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -42430,7 +42826,7 @@
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G307" t="n">
@@ -42490,7 +42886,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Randi Zuckerberg</t>
+          <t>THE GITEX Summit</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -42511,7 +42907,7 @@
       </c>
       <c r="F308" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G308" t="n">
@@ -42571,7 +42967,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Sean Garnier</t>
+          <t>TECH LEADERS</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -42592,7 +42988,7 @@
       </c>
       <c r="F309" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G309" t="n">
@@ -42652,7 +43048,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>Sean o'Sullivan</t>
+          <t>Gilberto Silva</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -42673,7 +43069,7 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G310" t="n">
@@ -42733,7 +43129,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Tej Lalvani</t>
+          <t>H.E. Alia Abdulla Al Mazrouei</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -42754,7 +43150,7 @@
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G311" t="n">
@@ -42814,7 +43210,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Vijay Shekhar Sharma</t>
+          <t>Jason Derulo</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -42835,7 +43231,7 @@
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -42895,7 +43291,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Dr. Guy Diedrich</t>
+          <t>Neil Patel</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -42916,7 +43312,7 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -42976,7 +43372,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>H.E. Omar Sultan Alolama</t>
+          <t>Peng Xiao</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -42997,7 +43393,7 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -43057,7 +43453,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>A.R. Rahman</t>
+          <t>Sean o'Sullivan</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -43078,7 +43474,7 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G315" t="n">
@@ -43138,7 +43534,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>David Cohen</t>
+          <t>H.E. Omar Sultan Alolama</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -43159,7 +43555,7 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G316" t="n">
@@ -43219,7 +43615,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Deep Nishar</t>
+          <t>Christian Weedbrook</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -43240,7 +43636,7 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G317" t="n">
@@ -43300,7 +43696,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Deepinder Goyal</t>
+          <t>Greg Jackson</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -43321,7 +43717,7 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G318" t="n">
@@ -43381,7 +43777,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Dr. Ghita Mezzour</t>
+          <t>Sir Martin Sorrell</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -43402,7 +43798,7 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G319" t="n">
@@ -43462,7 +43858,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Greg Jackson</t>
+          <t>Vinod Khosla</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -43483,7 +43879,7 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G320" t="n">
@@ -43543,7 +43939,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>Dr. Mactar Seck</t>
+          <t>EMIL SYUNDYUKOV</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -43564,7 +43960,7 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G321" t="n">
@@ -43624,7 +44020,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>H.E. Hamad Almansoori</t>
+          <t>MAYANK YADAV</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -43645,7 +44041,7 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G322" t="n">
@@ -43705,7 +44101,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>H.E. Ms. Mariam Al Mheiri</t>
+          <t>DAVID COHEN</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -43726,7 +44122,7 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G323" t="n">
@@ -43786,7 +44182,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Jack Selby</t>
+          <t>ZHONG XU</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -43807,7 +44203,7 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G324" t="n">
@@ -43867,7 +44263,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Sir Martin Sorrell</t>
+          <t>NAKUL GARG</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -43888,7 +44284,7 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G325" t="n">
@@ -43948,7 +44344,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Sir Tim Berners Lee</t>
+          <t>JANADE DU PLESSIS</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -43969,7 +44365,7 @@
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G326" t="n">
@@ -44029,7 +44425,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Vinod Khosla</t>
+          <t>GEOFFREY COSTILHES</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -44050,7 +44446,7 @@
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-12)</t>
+          <t>GITEX / Expand North Star Supernova Challenge (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G327" t="n">
@@ -44131,7 +44527,7 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G328" t="n">
@@ -44212,7 +44608,7 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G329" t="n">
@@ -44293,7 +44689,7 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G330" t="n">
@@ -44374,7 +44770,7 @@
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G331" t="n">
@@ -44455,7 +44851,7 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G332" t="n">
@@ -44536,7 +44932,7 @@
       </c>
       <c r="F333" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G333" t="n">
@@ -44617,7 +45013,7 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G334" t="n">
@@ -44698,7 +45094,7 @@
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G335" t="n">
@@ -44779,7 +45175,7 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G336" t="n">
@@ -44860,7 +45256,7 @@
       </c>
       <c r="F337" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G337" t="n">
@@ -44941,7 +45337,7 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>XPRIZE Winners (auto-discovered 2026-10-12)</t>
+          <t>XPRIZE Winners (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G338" t="n">
@@ -45022,7 +45418,7 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G339" t="n">
@@ -45103,7 +45499,7 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G340" t="n">
@@ -45184,7 +45580,7 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G341" t="n">
@@ -45265,7 +45661,7 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G342" t="n">
@@ -45346,7 +45742,7 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G343" t="n">
@@ -45427,7 +45823,7 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G344" t="n">
@@ -45508,7 +45904,7 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G345" t="n">
@@ -45589,7 +45985,7 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G346" t="n">
@@ -45670,7 +46066,7 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G347" t="n">
@@ -45751,7 +46147,7 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G348" t="n">
@@ -45832,7 +46228,7 @@
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G349" t="n">
@@ -45913,7 +46309,7 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G350" t="n">
@@ -45994,7 +46390,7 @@
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G351" t="n">
@@ -46075,7 +46471,7 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G352" t="n">
@@ -46156,7 +46552,7 @@
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G353" t="n">
@@ -46237,7 +46633,7 @@
       </c>
       <c r="F354" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G354" t="n">
@@ -46318,7 +46714,7 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G355" t="n">
@@ -46399,7 +46795,7 @@
       </c>
       <c r="F356" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G356" t="n">
@@ -46480,7 +46876,7 @@
       </c>
       <c r="F357" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G357" t="n">
@@ -46561,7 +46957,7 @@
       </c>
       <c r="F358" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G358" t="n">
@@ -46642,7 +47038,7 @@
       </c>
       <c r="F359" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G359" t="n">
@@ -46702,7 +47098,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>State of AI Q3’26</t>
+          <t>CEO Interview: Vitazi.ai</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -46723,7 +47119,7 @@
       </c>
       <c r="F360" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G360" t="n">
@@ -46783,7 +47179,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>The TradFi-DeFi Market Map</t>
+          <t>You might also like</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -46804,7 +47200,7 @@
       </c>
       <c r="F361" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>CB Insights AI 100 (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G361" t="n">
@@ -46864,7 +47260,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>You might also like</t>
+          <t>Accelerator Programme</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -46880,12 +47276,12 @@
       <c r="D362" t="inlineStr"/>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Editorial List</t>
+          <t>Gov/IGO Program</t>
         </is>
       </c>
       <c r="F362" t="inlineStr">
         <is>
-          <t>CB Insights AI 100 (auto-discovered 2026-10-12)</t>
+          <t>NATO DIANA Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G362" t="n">
@@ -46945,7 +47341,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>What is the EIC Accelerator ?</t>
+          <t>Challenges</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -46966,7 +47362,7 @@
       </c>
       <c r="F363" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>NATO DIANA Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G363" t="n">
@@ -47026,7 +47422,7 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>EIC Accelerator</t>
+          <t>Test centres</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -47047,7 +47443,7 @@
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>NATO DIANA Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G364" t="n">
@@ -47107,7 +47503,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Grant only</t>
+          <t>Business</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -47128,7 +47524,7 @@
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>NATO DIANA Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G365" t="n">
@@ -47188,7 +47584,7 @@
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Blended finance:</t>
+          <t>Capital Network</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -47209,7 +47605,7 @@
       </c>
       <c r="F366" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>NATO DIANA Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G366" t="n">
@@ -47269,7 +47665,7 @@
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Investment only:</t>
+          <t>Join our team</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -47290,7 +47686,7 @@
       </c>
       <c r="F367" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>NATO DIANA Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G367" t="n">
@@ -47350,7 +47746,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>Access to global partners</t>
+          <t>News</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -47371,7 +47767,7 @@
       </c>
       <c r="F368" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>NATO DIANA Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G368" t="n">
@@ -47431,7 +47827,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Access to coaches, mentors, expertise and training</t>
+          <t>Content &amp; Social</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -47452,7 +47848,7 @@
       </c>
       <c r="F369" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>NATO DIANA Innovators (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G369" t="n">
@@ -47512,7 +47908,7 @@
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>Access to innovation ecosystem and peers</t>
+          <t>What is the EIC Accelerator ?</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -47533,7 +47929,7 @@
       </c>
       <c r="F370" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G370" t="n">
@@ -47593,7 +47989,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Writing a short proposal</t>
+          <t>EIC Accelerator</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -47614,7 +48010,7 @@
       </c>
       <c r="F371" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G371" t="n">
@@ -47674,7 +48070,7 @@
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Submission of a full proposal</t>
+          <t>Grant only</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -47695,7 +48091,7 @@
       </c>
       <c r="F372" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G372" t="n">
@@ -47755,7 +48151,7 @@
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Face to face interview with the EIC Jury</t>
+          <t>Blended finance:</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -47776,7 +48172,7 @@
       </c>
       <c r="F373" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G373" t="n">
@@ -47836,7 +48232,7 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>EIC Jury</t>
+          <t>Investment only:</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -47857,7 +48253,7 @@
       </c>
       <c r="F374" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G374" t="n">
@@ -47917,7 +48313,7 @@
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>General publications</t>
+          <t>Access to global partners</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -47938,7 +48334,7 @@
       </c>
       <c r="F375" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G375" t="n">
@@ -47998,7 +48394,7 @@
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Who can apply?</t>
+          <t>Access to coaches, mentors, expertise and training</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -48019,7 +48415,7 @@
       </c>
       <c r="F376" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G376" t="n">
@@ -48079,7 +48475,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Single start-up or SME (including spin-outs)</t>
+          <t>Access to innovation ecosystem and peers</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -48100,7 +48496,7 @@
       </c>
       <c r="F377" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G377" t="n">
@@ -48160,7 +48556,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Applicants from third countries:</t>
+          <t>Writing a short proposal</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -48181,7 +48577,7 @@
       </c>
       <c r="F378" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G378" t="n">
@@ -48241,7 +48637,7 @@
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Concurrent applications:</t>
+          <t>Submission of a full proposal</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -48262,7 +48658,7 @@
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G379" t="n">
@@ -48322,7 +48718,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>A pitch-deck of up to ten slides in PDF format;</t>
+          <t>Face to face interview with the EIC Jury</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -48343,7 +48739,7 @@
       </c>
       <c r="F380" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G380" t="n">
@@ -48403,7 +48799,7 @@
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>Grant only:</t>
+          <t>EIC Jury</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -48424,7 +48820,7 @@
       </c>
       <c r="F381" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G381" t="n">
@@ -48484,7 +48880,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>General information</t>
+          <t>General publications</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -48505,7 +48901,7 @@
       </c>
       <c r="F382" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G382" t="n">
@@ -48565,7 +48961,7 @@
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>Direct submissions</t>
+          <t>Who can apply?</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -48586,7 +48982,7 @@
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G383" t="n">
@@ -48646,7 +49042,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Fast Track</t>
+          <t>Single start-up or SME (including spin-outs)</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -48667,7 +49063,7 @@
       </c>
       <c r="F384" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G384" t="n">
@@ -48727,7 +49123,7 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Plug-In</t>
+          <t>Applicants from third countries:</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -48748,7 +49144,7 @@
       </c>
       <c r="F385" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G385" t="n">
@@ -48808,7 +49204,7 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Do you need help ?</t>
+          <t>Concurrent applications:</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -48829,7 +49225,7 @@
       </c>
       <c r="F386" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G386" t="n">
@@ -48889,7 +49285,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>News</t>
+          <t>A pitch-deck of up to ten slides in PDF format;</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -48910,7 +49306,7 @@
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G387" t="n">
@@ -48970,7 +49366,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>News article</t>
+          <t>Grant only:</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -48991,7 +49387,7 @@
       </c>
       <c r="F388" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G388" t="n">
@@ -49051,7 +49447,7 @@
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Date</t>
+          <t>General information</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -49072,7 +49468,7 @@
       </c>
       <c r="F389" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G389" t="n">
@@ -49132,7 +49528,7 @@
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Language</t>
+          <t>Direct submissions</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -49153,7 +49549,7 @@
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-12)</t>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
         </is>
       </c>
       <c r="G390" t="n">
@@ -49205,6 +49601,735 @@
         </is>
       </c>
       <c r="S390" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Fast Track</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr"/>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>Gov/IGO Program</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
+        </is>
+      </c>
+      <c r="G391" t="n">
+        <v>5</v>
+      </c>
+      <c r="H391" t="n">
+        <v>0</v>
+      </c>
+      <c r="I391" t="n">
+        <v>0</v>
+      </c>
+      <c r="J391" t="n">
+        <v>0</v>
+      </c>
+      <c r="K391" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L391" t="n">
+        <v>0</v>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>Private/Unknown, award-cohort selection only, no disclosed funding stage</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>0 no financial performance data disclosed</t>
+        </is>
+      </c>
+      <c r="P391" t="inlineStr">
+        <is>
+          <t>0 no capital-backing detail disclosed</t>
+        </is>
+      </c>
+      <c r="Q391" t="inlineStr">
+        <is>
+          <t>0 no market-position evidence disclosed (selection alone is not market-leadership evidence)</t>
+        </is>
+      </c>
+      <c r="R391" t="inlineStr">
+        <is>
+          <t>-5 no disclosed liquidity timeline (data opacity)</t>
+        </is>
+      </c>
+      <c r="S391" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Plug-In</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr"/>
+      <c r="E392" t="inlineStr">
+        <is>
+          <t>Gov/IGO Program</t>
+        </is>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
+        </is>
+      </c>
+      <c r="G392" t="n">
+        <v>5</v>
+      </c>
+      <c r="H392" t="n">
+        <v>0</v>
+      </c>
+      <c r="I392" t="n">
+        <v>0</v>
+      </c>
+      <c r="J392" t="n">
+        <v>0</v>
+      </c>
+      <c r="K392" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L392" t="n">
+        <v>0</v>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>Private/Unknown, award-cohort selection only, no disclosed funding stage</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>0 no financial performance data disclosed</t>
+        </is>
+      </c>
+      <c r="P392" t="inlineStr">
+        <is>
+          <t>0 no capital-backing detail disclosed</t>
+        </is>
+      </c>
+      <c r="Q392" t="inlineStr">
+        <is>
+          <t>0 no market-position evidence disclosed (selection alone is not market-leadership evidence)</t>
+        </is>
+      </c>
+      <c r="R392" t="inlineStr">
+        <is>
+          <t>-5 no disclosed liquidity timeline (data opacity)</t>
+        </is>
+      </c>
+      <c r="S392" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Do you need help ?</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr"/>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>Gov/IGO Program</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
+        </is>
+      </c>
+      <c r="G393" t="n">
+        <v>5</v>
+      </c>
+      <c r="H393" t="n">
+        <v>0</v>
+      </c>
+      <c r="I393" t="n">
+        <v>0</v>
+      </c>
+      <c r="J393" t="n">
+        <v>0</v>
+      </c>
+      <c r="K393" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L393" t="n">
+        <v>0</v>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>Private/Unknown, award-cohort selection only, no disclosed funding stage</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>0 no financial performance data disclosed</t>
+        </is>
+      </c>
+      <c r="P393" t="inlineStr">
+        <is>
+          <t>0 no capital-backing detail disclosed</t>
+        </is>
+      </c>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>0 no market-position evidence disclosed (selection alone is not market-leadership evidence)</t>
+        </is>
+      </c>
+      <c r="R393" t="inlineStr">
+        <is>
+          <t>-5 no disclosed liquidity timeline (data opacity)</t>
+        </is>
+      </c>
+      <c r="S393" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr"/>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>Gov/IGO Program</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
+        </is>
+      </c>
+      <c r="G394" t="n">
+        <v>5</v>
+      </c>
+      <c r="H394" t="n">
+        <v>0</v>
+      </c>
+      <c r="I394" t="n">
+        <v>0</v>
+      </c>
+      <c r="J394" t="n">
+        <v>0</v>
+      </c>
+      <c r="K394" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L394" t="n">
+        <v>0</v>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>Private/Unknown, award-cohort selection only, no disclosed funding stage</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>0 no financial performance data disclosed</t>
+        </is>
+      </c>
+      <c r="P394" t="inlineStr">
+        <is>
+          <t>0 no capital-backing detail disclosed</t>
+        </is>
+      </c>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>0 no market-position evidence disclosed (selection alone is not market-leadership evidence)</t>
+        </is>
+      </c>
+      <c r="R394" t="inlineStr">
+        <is>
+          <t>-5 no disclosed liquidity timeline (data opacity)</t>
+        </is>
+      </c>
+      <c r="S394" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>News article</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr"/>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>Gov/IGO Program</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
+        </is>
+      </c>
+      <c r="G395" t="n">
+        <v>5</v>
+      </c>
+      <c r="H395" t="n">
+        <v>0</v>
+      </c>
+      <c r="I395" t="n">
+        <v>0</v>
+      </c>
+      <c r="J395" t="n">
+        <v>0</v>
+      </c>
+      <c r="K395" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L395" t="n">
+        <v>0</v>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>Private/Unknown, award-cohort selection only, no disclosed funding stage</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>0 no financial performance data disclosed</t>
+        </is>
+      </c>
+      <c r="P395" t="inlineStr">
+        <is>
+          <t>0 no capital-backing detail disclosed</t>
+        </is>
+      </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>0 no market-position evidence disclosed (selection alone is not market-leadership evidence)</t>
+        </is>
+      </c>
+      <c r="R395" t="inlineStr">
+        <is>
+          <t>-5 no disclosed liquidity timeline (data opacity)</t>
+        </is>
+      </c>
+      <c r="S395" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Events</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr"/>
+      <c r="E396" t="inlineStr">
+        <is>
+          <t>Gov/IGO Program</t>
+        </is>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
+        </is>
+      </c>
+      <c r="G396" t="n">
+        <v>5</v>
+      </c>
+      <c r="H396" t="n">
+        <v>0</v>
+      </c>
+      <c r="I396" t="n">
+        <v>0</v>
+      </c>
+      <c r="J396" t="n">
+        <v>0</v>
+      </c>
+      <c r="K396" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L396" t="n">
+        <v>0</v>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>Private/Unknown, award-cohort selection only, no disclosed funding stage</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>0 no financial performance data disclosed</t>
+        </is>
+      </c>
+      <c r="P396" t="inlineStr">
+        <is>
+          <t>0 no capital-backing detail disclosed</t>
+        </is>
+      </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>0 no market-position evidence disclosed (selection alone is not market-leadership evidence)</t>
+        </is>
+      </c>
+      <c r="R396" t="inlineStr">
+        <is>
+          <t>-5 no disclosed liquidity timeline (data opacity)</t>
+        </is>
+      </c>
+      <c r="S396" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Online only</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr"/>
+      <c r="E397" t="inlineStr">
+        <is>
+          <t>Gov/IGO Program</t>
+        </is>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
+        </is>
+      </c>
+      <c r="G397" t="n">
+        <v>5</v>
+      </c>
+      <c r="H397" t="n">
+        <v>0</v>
+      </c>
+      <c r="I397" t="n">
+        <v>0</v>
+      </c>
+      <c r="J397" t="n">
+        <v>0</v>
+      </c>
+      <c r="K397" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L397" t="n">
+        <v>0</v>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>Private/Unknown, award-cohort selection only, no disclosed funding stage</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>0 no financial performance data disclosed</t>
+        </is>
+      </c>
+      <c r="P397" t="inlineStr">
+        <is>
+          <t>0 no capital-backing detail disclosed</t>
+        </is>
+      </c>
+      <c r="Q397" t="inlineStr">
+        <is>
+          <t>0 no market-position evidence disclosed (selection alone is not market-leadership evidence)</t>
+        </is>
+      </c>
+      <c r="R397" t="inlineStr">
+        <is>
+          <t>-5 no disclosed liquidity timeline (data opacity)</t>
+        </is>
+      </c>
+      <c r="S397" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr"/>
+      <c r="E398" t="inlineStr">
+        <is>
+          <t>Gov/IGO Program</t>
+        </is>
+      </c>
+      <c r="F398" t="inlineStr">
+        <is>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
+        </is>
+      </c>
+      <c r="G398" t="n">
+        <v>5</v>
+      </c>
+      <c r="H398" t="n">
+        <v>0</v>
+      </c>
+      <c r="I398" t="n">
+        <v>0</v>
+      </c>
+      <c r="J398" t="n">
+        <v>0</v>
+      </c>
+      <c r="K398" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L398" t="n">
+        <v>0</v>
+      </c>
+      <c r="M398" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="N398" t="inlineStr">
+        <is>
+          <t>Private/Unknown, award-cohort selection only, no disclosed funding stage</t>
+        </is>
+      </c>
+      <c r="O398" t="inlineStr">
+        <is>
+          <t>0 no financial performance data disclosed</t>
+        </is>
+      </c>
+      <c r="P398" t="inlineStr">
+        <is>
+          <t>0 no capital-backing detail disclosed</t>
+        </is>
+      </c>
+      <c r="Q398" t="inlineStr">
+        <is>
+          <t>0 no market-position evidence disclosed (selection alone is not market-leadership evidence)</t>
+        </is>
+      </c>
+      <c r="R398" t="inlineStr">
+        <is>
+          <t>-5 no disclosed liquidity timeline (data opacity)</t>
+        </is>
+      </c>
+      <c r="S398" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Language</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr"/>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>Gov/IGO Program</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr">
+        <is>
+          <t>EU EIC Accelerator Companies (auto-discovered 2026-10-19)</t>
+        </is>
+      </c>
+      <c r="G399" t="n">
+        <v>5</v>
+      </c>
+      <c r="H399" t="n">
+        <v>0</v>
+      </c>
+      <c r="I399" t="n">
+        <v>0</v>
+      </c>
+      <c r="J399" t="n">
+        <v>0</v>
+      </c>
+      <c r="K399" t="n">
+        <v>-5</v>
+      </c>
+      <c r="L399" t="n">
+        <v>0</v>
+      </c>
+      <c r="M399" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="N399" t="inlineStr">
+        <is>
+          <t>Private/Unknown, award-cohort selection only, no disclosed funding stage</t>
+        </is>
+      </c>
+      <c r="O399" t="inlineStr">
+        <is>
+          <t>0 no financial performance data disclosed</t>
+        </is>
+      </c>
+      <c r="P399" t="inlineStr">
+        <is>
+          <t>0 no capital-backing detail disclosed</t>
+        </is>
+      </c>
+      <c r="Q399" t="inlineStr">
+        <is>
+          <t>0 no market-position evidence disclosed (selection alone is not market-leadership evidence)</t>
+        </is>
+      </c>
+      <c r="R399" t="inlineStr">
+        <is>
+          <t>-5 no disclosed liquidity timeline (data opacity)</t>
+        </is>
+      </c>
+      <c r="S399" t="inlineStr">
         <is>
           <t>No</t>
         </is>
@@ -49274,7 +50399,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-10-12T22:27:14.987352+00:00</t>
+          <t>2026-10-19T20:29:16.237061+00:00</t>
         </is>
       </c>
     </row>
@@ -49301,7 +50426,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-10-12T22:27:22.512101+00:00</t>
+          <t>2026-10-19T20:29:26.127349+00:00</t>
         </is>
       </c>
     </row>
@@ -49328,7 +50453,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-10-12T22:27:44.342069+00:00</t>
+          <t>2026-10-19T20:29:46.330579+00:00</t>
         </is>
       </c>
     </row>
@@ -49355,7 +50480,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-10-12T22:28:12.973842+00:00</t>
+          <t>2026-10-19T20:29:56.162714+00:00</t>
         </is>
       </c>
     </row>
@@ -49382,7 +50507,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-10-12T22:28:18.049935+00:00</t>
+          <t>2026-10-19T20:30:02.699873+00:00</t>
         </is>
       </c>
     </row>
@@ -49409,7 +50534,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-10-12T22:28:19.486142+00:00</t>
+          <t>2026-10-19T20:30:04.367022+00:00</t>
         </is>
       </c>
     </row>
@@ -49436,7 +50561,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-10-12T22:28:19.595145+00:00</t>
+          <t>2026-10-19T20:30:04.591974+00:00</t>
         </is>
       </c>
     </row>
@@ -49463,7 +50588,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-10-12T22:28:19.839507+00:00</t>
+          <t>2026-10-19T20:30:08.553290+00:00</t>
         </is>
       </c>
     </row>
@@ -49490,7 +50615,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-10-12T22:28:24.003314+00:00</t>
+          <t>2026-10-19T20:30:12.491190+00:00</t>
         </is>
       </c>
     </row>
@@ -49520,7 +50645,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-10-12T22:28:28.489164+00:00</t>
+          <t>2026-10-19T20:30:30.040396+00:00</t>
         </is>
       </c>
     </row>
@@ -49542,12 +50667,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OK: 78 candidate entities extracted (browser fetch: 78 candidates) — unverified, review before treating as ground truth</t>
+          <t>OK: 40 candidate entities extracted (browser fetch: 40 candidates) — unverified, review before treating as ground truth</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-10-12T22:28:58.997998+00:00</t>
+          <t>2026-10-19T20:31:00.432931+00:00</t>
         </is>
       </c>
     </row>
@@ -49577,7 +50702,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-10-12T22:29:08.628347+00:00</t>
+          <t>2026-10-19T20:31:15.127944+00:00</t>
         </is>
       </c>
     </row>
@@ -49604,7 +50729,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-10-12T22:29:39.118805+00:00</t>
+          <t>2026-10-19T20:31:45.457062+00:00</t>
         </is>
       </c>
     </row>
@@ -49631,7 +50756,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-10-12T22:29:43.538441+00:00</t>
+          <t>2026-10-19T20:31:49.951927+00:00</t>
         </is>
       </c>
     </row>
@@ -49661,7 +50786,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-10-12T22:29:47.107204+00:00</t>
+          <t>2026-10-19T20:31:53.446263+00:00</t>
         </is>
       </c>
     </row>
@@ -49691,7 +50816,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-10-12T22:30:17.644096+00:00</t>
+          <t>2026-10-19T20:32:24.316409+00:00</t>
         </is>
       </c>
     </row>
@@ -49718,7 +50843,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-10-12T22:30:48.331379+00:00</t>
+          <t>2026-10-19T20:32:54.814448+00:00</t>
         </is>
       </c>
     </row>
@@ -49740,12 +50865,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>OK: 24 candidate entities extracted (browser fetch: 24 candidates) — unverified, review before treating as ground truth</t>
+          <t>OK: 23 candidate entities extracted (browser fetch: 23 candidates) — unverified, review before treating as ground truth</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-10-12T22:30:51.311548+00:00</t>
+          <t>2026-10-19T20:32:57.966354+00:00</t>
         </is>
       </c>
     </row>
@@ -49767,15 +50892,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NEEDS_REVIEW: browser fetch failed (playwright error: Page.goto: Timeout 30000ms exceeded.
-Call log:
-  - navigating to "https://www.diana.nato.int/", waiting until "networkidle"
-) — page likely doesn't list entities directly, or is blocked.</t>
+          <t>OK: 8 candidate entities extracted (browser fetch: 8 candidates) — unverified, review before treating as ground truth</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-10-12T22:30:58.160486+00:00</t>
+          <t>2026-10-19T20:33:05.231720+00:00</t>
         </is>
       </c>
     </row>
@@ -49802,7 +50924,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-10-12T22:31:28.648677+00:00</t>
+          <t>2026-10-19T20:33:08.893336+00:00</t>
         </is>
       </c>
     </row>
@@ -49824,12 +50946,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>OK: 28 candidate entities extracted (browser fetch: 28 candidates) — unverified, review before treating as ground truth</t>
+          <t>OK: 30 candidate entities extracted (browser fetch: 30 candidates) — unverified, review before treating as ground truth</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-10-12T22:31:32.545927+00:00</t>
+          <t>2026-10-19T20:33:14.872769+00:00</t>
         </is>
       </c>
     </row>
